--- a/Data/EXCEL/Transfer/salemon/20240711/3687-salemon-20240711.xlsx
+++ b/Data/EXCEL/Transfer/salemon/20240711/3687-salemon-20240711.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlsx\20240711\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\GithubProjects\GoodinfoData2DB\Data\EXCEL\Transfer\salemon\20240711\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F88D8424-DBE9-4FFB-BA66-D6A6E0A3976E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{6A68F0ED-6A4C-4AF6-955A-F9F0C010284D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="900" yWindow="290" windowWidth="18240" windowHeight="13390" xr2:uid="{BD207F61-51E8-45A2-9A63-D0005CF98674}"/>
+    <workbookView xWindow="768" yWindow="684" windowWidth="20004" windowHeight="13956" xr2:uid="{E376DABA-769F-43A9-A3EE-70CDA6A5AC6D}"/>
   </bookViews>
   <sheets>
     <sheet name="3687-salemon-20240711" sheetId="2" r:id="rId1"/>
@@ -1261,19 +1261,19 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{671D9963-3E01-4C9C-80F3-A2FCB7C5504A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{68D70BB4-BCB5-40EA-9148-65C28AAA7C7B}">
   <dimension ref="A1:Q366"/>
-  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="6.54296875" bestFit="1" customWidth="1"/>
-    <col min="2" max="6" width="5.36328125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="5.90625" bestFit="1" customWidth="1"/>
-    <col min="8" max="13" width="5.36328125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="5.08984375" bestFit="1" customWidth="1"/>
-    <col min="15" max="17" width="5.36328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="6" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="13" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="15" max="17" width="5.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A1" s="15" t="s">
         <v>0</v>
       </c>
@@ -1300,7 +1300,7 @@
       <c r="P1" s="19"/>
       <c r="Q1" s="20"/>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A2" s="16"/>
       <c r="B2" s="15" t="s">
         <v>4</v>
@@ -1339,7 +1339,7 @@
       </c>
       <c r="Q2" s="20"/>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A3" s="16"/>
       <c r="B3" s="16"/>
       <c r="C3" s="16"/>
@@ -1382,7 +1382,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A4" s="17"/>
       <c r="B4" s="17"/>
       <c r="C4" s="17"/>
@@ -1421,7 +1421,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A5" s="5">
         <v>45444</v>
       </c>
@@ -1474,7 +1474,7 @@
         <v>5.34</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A6" s="10">
         <v>45413</v>
       </c>
@@ -1527,7 +1527,7 @@
         <v>5.27</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A7" s="5">
         <v>45383</v>
       </c>
@@ -1580,7 +1580,7 @@
         <v>6.57</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A8" s="10">
         <v>45352</v>
       </c>
@@ -1633,7 +1633,7 @@
         <v>3.73</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A9" s="5">
         <v>45323</v>
       </c>
@@ -1686,7 +1686,7 @@
         <v>11.6</v>
       </c>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A10" s="10">
         <v>45292</v>
       </c>
@@ -1739,7 +1739,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A11" s="5">
         <v>45261</v>
       </c>
@@ -1792,7 +1792,7 @@
         <v>-2.72</v>
       </c>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A12" s="10">
         <v>45231</v>
       </c>
@@ -1845,7 +1845,7 @@
         <v>-3.13</v>
       </c>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A13" s="5">
         <v>45200</v>
       </c>
@@ -1898,7 +1898,7 @@
         <v>-3.53</v>
       </c>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A14" s="10">
         <v>45170</v>
       </c>
@@ -1951,7 +1951,7 @@
         <v>-4.04</v>
       </c>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A15" s="5">
         <v>45139</v>
       </c>
@@ -2004,7 +2004,7 @@
         <v>-4.3899999999999997</v>
       </c>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A16" s="10">
         <v>45108</v>
       </c>
@@ -2057,7 +2057,7 @@
         <v>-4.2699999999999996</v>
       </c>
     </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A17" s="5">
         <v>45078</v>
       </c>
@@ -2110,7 +2110,7 @@
         <v>-5.44</v>
       </c>
     </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A18" s="10">
         <v>45047</v>
       </c>
@@ -2163,7 +2163,7 @@
         <v>-1.71</v>
       </c>
     </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A19" s="5">
         <v>45017</v>
       </c>
@@ -2216,7 +2216,7 @@
         <v>-2.38</v>
       </c>
     </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A20" s="10">
         <v>44986</v>
       </c>
@@ -2269,7 +2269,7 @@
         <v>-0.7</v>
       </c>
     </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A21" s="5">
         <v>44958</v>
       </c>
@@ -2322,7 +2322,7 @@
         <v>-3.59</v>
       </c>
     </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A22" s="10">
         <v>44927</v>
       </c>
@@ -2375,7 +2375,7 @@
         <v>-7.62</v>
       </c>
     </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A23" s="5">
         <v>44896</v>
       </c>
@@ -2428,7 +2428,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A24" s="10">
         <v>44866</v>
       </c>
@@ -2481,7 +2481,7 @@
         <v>6.16</v>
       </c>
     </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A25" s="5">
         <v>44835</v>
       </c>
@@ -2534,7 +2534,7 @@
         <v>7.04</v>
       </c>
     </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A26" s="10">
         <v>44805</v>
       </c>
@@ -2587,7 +2587,7 @@
         <v>6.7</v>
       </c>
     </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A27" s="5">
         <v>44774</v>
       </c>
@@ -2640,7 +2640,7 @@
         <v>6.99</v>
       </c>
     </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A28" s="10">
         <v>44743</v>
       </c>
@@ -2693,7 +2693,7 @@
         <v>7.88</v>
       </c>
     </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A29" s="5">
         <v>44713</v>
       </c>
@@ -2746,7 +2746,7 @@
         <v>12.1</v>
       </c>
     </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A30" s="10">
         <v>44682</v>
       </c>
@@ -2799,7 +2799,7 @@
         <v>12.6</v>
       </c>
     </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A31" s="5">
         <v>44652</v>
       </c>
@@ -2852,7 +2852,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A32" s="10">
         <v>44621</v>
       </c>
@@ -2905,7 +2905,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A33" s="5">
         <v>44593</v>
       </c>
@@ -2958,7 +2958,7 @@
         <v>14.4</v>
       </c>
     </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A34" s="10">
         <v>44562</v>
       </c>
@@ -3011,7 +3011,7 @@
         <v>18.2</v>
       </c>
     </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A35" s="5">
         <v>44531</v>
       </c>
@@ -3064,7 +3064,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A36" s="10">
         <v>44501</v>
       </c>
@@ -3117,7 +3117,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A37" s="5">
         <v>44470</v>
       </c>
@@ -3170,7 +3170,7 @@
         <v>31.1</v>
       </c>
     </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A38" s="10">
         <v>44440</v>
       </c>
@@ -3223,7 +3223,7 @@
         <v>32.200000000000003</v>
       </c>
     </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A39" s="5">
         <v>44409</v>
       </c>
@@ -3276,7 +3276,7 @@
         <v>34.299999999999997</v>
       </c>
     </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A40" s="10">
         <v>44378</v>
       </c>
@@ -3329,7 +3329,7 @@
         <v>34.799999999999997</v>
       </c>
     </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A41" s="5">
         <v>44348</v>
       </c>
@@ -3382,7 +3382,7 @@
         <v>33.6</v>
       </c>
     </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A42" s="10">
         <v>44317</v>
       </c>
@@ -3435,7 +3435,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A43" s="5">
         <v>44287</v>
       </c>
@@ -3488,7 +3488,7 @@
         <v>16.600000000000001</v>
       </c>
     </row>
-    <row r="44" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A44" s="10">
         <v>44256</v>
       </c>
@@ -3541,7 +3541,7 @@
         <v>17.5</v>
       </c>
     </row>
-    <row r="45" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A45" s="5">
         <v>44228</v>
       </c>
@@ -3594,7 +3594,7 @@
         <v>17.100000000000001</v>
       </c>
     </row>
-    <row r="46" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A46" s="10">
         <v>44197</v>
       </c>
@@ -3647,7 +3647,7 @@
         <v>21.3</v>
       </c>
     </row>
-    <row r="47" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A47" s="5">
         <v>44166</v>
       </c>
@@ -3700,7 +3700,7 @@
         <v>13.1</v>
       </c>
     </row>
-    <row r="48" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A48" s="10">
         <v>44136</v>
       </c>
@@ -3753,7 +3753,7 @@
         <v>13.7</v>
       </c>
     </row>
-    <row r="49" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A49" s="5">
         <v>44105</v>
       </c>
@@ -3806,7 +3806,7 @@
         <v>12.9</v>
       </c>
     </row>
-    <row r="50" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A50" s="10">
         <v>44075</v>
       </c>
@@ -3859,7 +3859,7 @@
         <v>13.9</v>
       </c>
     </row>
-    <row r="51" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A51" s="5">
         <v>44044</v>
       </c>
@@ -3912,7 +3912,7 @@
         <v>12.3</v>
       </c>
     </row>
-    <row r="52" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A52" s="10">
         <v>44013</v>
       </c>
@@ -3965,7 +3965,7 @@
         <v>10.5</v>
       </c>
     </row>
-    <row r="53" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A53" s="5">
         <v>43983</v>
       </c>
@@ -4018,7 +4018,7 @@
         <v>10.199999999999999</v>
       </c>
     </row>
-    <row r="54" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A54" s="10">
         <v>43952</v>
       </c>
@@ -4071,7 +4071,7 @@
         <v>7.62</v>
       </c>
     </row>
-    <row r="55" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="55" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A55" s="5">
         <v>43922</v>
       </c>
@@ -4124,7 +4124,7 @@
         <v>18.899999999999999</v>
       </c>
     </row>
-    <row r="56" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="56" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A56" s="10">
         <v>43891</v>
       </c>
@@ -4177,7 +4177,7 @@
         <v>21.4</v>
       </c>
     </row>
-    <row r="57" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="57" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A57" s="5">
         <v>43862</v>
       </c>
@@ -4230,7 +4230,7 @@
         <v>18.8</v>
       </c>
     </row>
-    <row r="58" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="58" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A58" s="10">
         <v>43831</v>
       </c>
@@ -4283,7 +4283,7 @@
         <v>11.3</v>
       </c>
     </row>
-    <row r="59" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="59" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A59" s="5">
         <v>43800</v>
       </c>
@@ -4336,7 +4336,7 @@
         <v>37.799999999999997</v>
       </c>
     </row>
-    <row r="60" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="60" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A60" s="10">
         <v>43770</v>
       </c>
@@ -4389,7 +4389,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="61" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="61" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A61" s="5">
         <v>43739</v>
       </c>
@@ -4442,7 +4442,7 @@
         <v>37.6</v>
       </c>
     </row>
-    <row r="62" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="62" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A62" s="10">
         <v>43709</v>
       </c>
@@ -4495,7 +4495,7 @@
         <v>37.4</v>
       </c>
     </row>
-    <row r="63" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="63" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A63" s="5">
         <v>43678</v>
       </c>
@@ -4548,7 +4548,7 @@
         <v>36.799999999999997</v>
       </c>
     </row>
-    <row r="64" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="64" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A64" s="10">
         <v>43647</v>
       </c>
@@ -4601,7 +4601,7 @@
         <v>35.9</v>
       </c>
     </row>
-    <row r="65" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="65" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A65" s="5">
         <v>43617</v>
       </c>
@@ -4654,7 +4654,7 @@
         <v>34.4</v>
       </c>
     </row>
-    <row r="66" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="66" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A66" s="10">
         <v>43586</v>
       </c>
@@ -4707,7 +4707,7 @@
         <v>34.5</v>
       </c>
     </row>
-    <row r="67" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="67" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A67" s="5">
         <v>43556</v>
       </c>
@@ -4760,7 +4760,7 @@
         <v>37.4</v>
       </c>
     </row>
-    <row r="68" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="68" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A68" s="10">
         <v>43525</v>
       </c>
@@ -4813,7 +4813,7 @@
         <v>41.4</v>
       </c>
     </row>
-    <row r="69" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="69" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A69" s="5">
         <v>43497</v>
       </c>
@@ -4866,7 +4866,7 @@
         <v>40.799999999999997</v>
       </c>
     </row>
-    <row r="70" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="70" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A70" s="10">
         <v>43466</v>
       </c>
@@ -4919,7 +4919,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="71" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="71" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A71" s="5">
         <v>43435</v>
       </c>
@@ -4972,7 +4972,7 @@
         <v>-11.5</v>
       </c>
     </row>
-    <row r="72" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="72" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A72" s="10">
         <v>43405</v>
       </c>
@@ -5025,7 +5025,7 @@
         <v>-14</v>
       </c>
     </row>
-    <row r="73" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="73" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A73" s="5">
         <v>43374</v>
       </c>
@@ -5078,7 +5078,7 @@
         <v>-17</v>
       </c>
     </row>
-    <row r="74" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="74" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A74" s="10">
         <v>43344</v>
       </c>
@@ -5131,7 +5131,7 @@
         <v>-20.100000000000001</v>
       </c>
     </row>
-    <row r="75" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="75" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A75" s="5">
         <v>43313</v>
       </c>
@@ -5184,7 +5184,7 @@
         <v>-22.6</v>
       </c>
     </row>
-    <row r="76" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="76" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A76" s="10">
         <v>43282</v>
       </c>
@@ -5237,7 +5237,7 @@
         <v>-24.5</v>
       </c>
     </row>
-    <row r="77" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="77" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A77" s="5">
         <v>43252</v>
       </c>
@@ -5290,7 +5290,7 @@
         <v>-26.6</v>
       </c>
     </row>
-    <row r="78" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="78" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A78" s="10">
         <v>43221</v>
       </c>
@@ -5343,7 +5343,7 @@
         <v>-28.7</v>
       </c>
     </row>
-    <row r="79" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="79" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A79" s="5">
         <v>43191</v>
       </c>
@@ -5396,7 +5396,7 @@
         <v>-32.299999999999997</v>
       </c>
     </row>
-    <row r="80" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="80" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A80" s="10">
         <v>43160</v>
       </c>
@@ -5449,7 +5449,7 @@
         <v>-35.1</v>
       </c>
     </row>
-    <row r="81" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="81" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A81" s="5">
         <v>43132</v>
       </c>
@@ -5502,7 +5502,7 @@
         <v>-19.2</v>
       </c>
     </row>
-    <row r="82" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="82" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A82" s="10">
         <v>43101</v>
       </c>
@@ -5555,7 +5555,7 @@
         <v>-1.99</v>
       </c>
     </row>
-    <row r="83" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="83" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A83" s="5">
         <v>43070</v>
       </c>
@@ -5608,7 +5608,7 @@
         <v>-5.55</v>
       </c>
     </row>
-    <row r="84" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="84" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A84" s="10">
         <v>43040</v>
       </c>
@@ -5661,7 +5661,7 @@
         <v>-3.78</v>
       </c>
     </row>
-    <row r="85" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="85" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A85" s="5">
         <v>43009</v>
       </c>
@@ -5714,7 +5714,7 @@
         <v>-3.37</v>
       </c>
     </row>
-    <row r="86" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="86" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A86" s="10">
         <v>42979</v>
       </c>
@@ -5767,7 +5767,7 @@
         <v>-2.48</v>
       </c>
     </row>
-    <row r="87" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="87" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A87" s="5">
         <v>42948</v>
       </c>
@@ -5820,7 +5820,7 @@
         <v>0.11</v>
       </c>
     </row>
-    <row r="88" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="88" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A88" s="10">
         <v>42917</v>
       </c>
@@ -5873,7 +5873,7 @@
         <v>6.04</v>
       </c>
     </row>
-    <row r="89" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="89" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A89" s="5">
         <v>42887</v>
       </c>
@@ -5926,7 +5926,7 @@
         <v>16.5</v>
       </c>
     </row>
-    <row r="90" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="90" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A90" s="10">
         <v>42856</v>
       </c>
@@ -5979,7 +5979,7 @@
         <v>18.7</v>
       </c>
     </row>
-    <row r="91" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="91" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A91" s="5">
         <v>42826</v>
       </c>
@@ -6032,7 +6032,7 @@
         <v>19.2</v>
       </c>
     </row>
-    <row r="92" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="92" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A92" s="10">
         <v>42795</v>
       </c>
@@ -6085,7 +6085,7 @@
         <v>14.3</v>
       </c>
     </row>
-    <row r="93" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="93" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A93" s="5">
         <v>42767</v>
       </c>
@@ -6138,7 +6138,7 @@
         <v>-7.39</v>
       </c>
     </row>
-    <row r="94" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="94" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A94" s="10">
         <v>42736</v>
       </c>
@@ -6191,7 +6191,7 @@
         <v>-4.42</v>
       </c>
     </row>
-    <row r="95" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="95" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A95" s="5">
         <v>42705</v>
       </c>
@@ -6244,7 +6244,7 @@
         <v>18.399999999999999</v>
       </c>
     </row>
-    <row r="96" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="96" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A96" s="10">
         <v>42675</v>
       </c>
@@ -6297,7 +6297,7 @@
         <v>24.8</v>
       </c>
     </row>
-    <row r="97" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="97" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A97" s="5">
         <v>42644</v>
       </c>
@@ -6350,7 +6350,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="98" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="98" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A98" s="10">
         <v>42614</v>
       </c>
@@ -6403,7 +6403,7 @@
         <v>32.700000000000003</v>
       </c>
     </row>
-    <row r="99" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="99" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A99" s="5">
         <v>42583</v>
       </c>
@@ -6456,7 +6456,7 @@
         <v>33.200000000000003</v>
       </c>
     </row>
-    <row r="100" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="100" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A100" s="10">
         <v>42552</v>
       </c>
@@ -6509,7 +6509,7 @@
         <v>30.7</v>
       </c>
     </row>
-    <row r="101" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="101" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A101" s="5">
         <v>42522</v>
       </c>
@@ -6562,7 +6562,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="102" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="102" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A102" s="10">
         <v>42491</v>
       </c>
@@ -6615,7 +6615,7 @@
         <v>29.7</v>
       </c>
     </row>
-    <row r="103" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="103" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A103" s="5">
         <v>42461</v>
       </c>
@@ -6668,7 +6668,7 @@
         <v>38.9</v>
       </c>
     </row>
-    <row r="104" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="104" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A104" s="10">
         <v>42430</v>
       </c>
@@ -6721,7 +6721,7 @@
         <v>61.8</v>
       </c>
     </row>
-    <row r="105" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="105" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A105" s="5">
         <v>42401</v>
       </c>
@@ -6774,7 +6774,7 @@
         <v>104.6</v>
       </c>
     </row>
-    <row r="106" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="106" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A106" s="10">
         <v>42370</v>
       </c>
@@ -6827,7 +6827,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="107" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="107" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A107" s="5">
         <v>42339</v>
       </c>
@@ -6880,7 +6880,7 @@
         <v>112.8</v>
       </c>
     </row>
-    <row r="108" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="108" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A108" s="10">
         <v>42309</v>
       </c>
@@ -6933,7 +6933,7 @@
         <v>103.4</v>
       </c>
     </row>
-    <row r="109" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="109" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A109" s="5">
         <v>42278</v>
       </c>
@@ -6986,7 +6986,7 @@
         <v>103.5</v>
       </c>
     </row>
-    <row r="110" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="110" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A110" s="10">
         <v>42248</v>
       </c>
@@ -7039,7 +7039,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="111" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="111" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A111" s="5">
         <v>42217</v>
       </c>
@@ -7092,7 +7092,7 @@
         <v>101.8</v>
       </c>
     </row>
-    <row r="112" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="112" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A112" s="10">
         <v>42186</v>
       </c>
@@ -7145,7 +7145,7 @@
         <v>101.3</v>
       </c>
     </row>
-    <row r="113" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="113" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A113" s="5">
         <v>42156</v>
       </c>
@@ -7198,7 +7198,7 @@
         <v>101.2</v>
       </c>
     </row>
-    <row r="114" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="114" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A114" s="10">
         <v>42125</v>
       </c>
@@ -7251,7 +7251,7 @@
         <v>105.9</v>
       </c>
     </row>
-    <row r="115" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="115" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A115" s="5">
         <v>42095</v>
       </c>
@@ -7304,7 +7304,7 @@
         <v>116.3</v>
       </c>
     </row>
-    <row r="116" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="116" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A116" s="10">
         <v>42064</v>
       </c>
@@ -7357,7 +7357,7 @@
         <v>118.8</v>
       </c>
     </row>
-    <row r="117" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="117" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A117" s="5">
         <v>42036</v>
       </c>
@@ -7410,7 +7410,7 @@
         <v>87.8</v>
       </c>
     </row>
-    <row r="118" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="118" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A118" s="10">
         <v>42005</v>
       </c>
@@ -7463,7 +7463,7 @@
         <v>45.3</v>
       </c>
     </row>
-    <row r="119" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="119" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A119" s="5">
         <v>41974</v>
       </c>
@@ -7516,7 +7516,7 @@
         <v>2.31</v>
       </c>
     </row>
-    <row r="120" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="120" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A120" s="10">
         <v>41944</v>
       </c>
@@ -7569,7 +7569,7 @@
         <v>-2.48</v>
       </c>
     </row>
-    <row r="121" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="121" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A121" s="5">
         <v>41913</v>
       </c>
@@ -7622,7 +7622,7 @@
         <v>-8.34</v>
       </c>
     </row>
-    <row r="122" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="122" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A122" s="10">
         <v>41883</v>
       </c>
@@ -7675,7 +7675,7 @@
         <v>-11.6</v>
       </c>
     </row>
-    <row r="123" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="123" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A123" s="5">
         <v>41852</v>
       </c>
@@ -7728,7 +7728,7 @@
         <v>-15.6</v>
       </c>
     </row>
-    <row r="124" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="124" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A124" s="10">
         <v>41821</v>
       </c>
@@ -7781,7 +7781,7 @@
         <v>-19</v>
       </c>
     </row>
-    <row r="125" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="125" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A125" s="5">
         <v>41791</v>
       </c>
@@ -7834,7 +7834,7 @@
         <v>-25.9</v>
       </c>
     </row>
-    <row r="126" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="126" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A126" s="10">
         <v>41760</v>
       </c>
@@ -7887,7 +7887,7 @@
         <v>-35.9</v>
       </c>
     </row>
-    <row r="127" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="127" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A127" s="5">
         <v>41730</v>
       </c>
@@ -7940,7 +7940,7 @@
         <v>-48</v>
       </c>
     </row>
-    <row r="128" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="128" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A128" s="10">
         <v>41699</v>
       </c>
@@ -7993,7 +7993,7 @@
         <v>-58.1</v>
       </c>
     </row>
-    <row r="129" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="129" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A129" s="5">
         <v>41671</v>
       </c>
@@ -8046,7 +8046,7 @@
         <v>-67.2</v>
       </c>
     </row>
-    <row r="130" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="130" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A130" s="10">
         <v>41640</v>
       </c>
@@ -8099,7 +8099,7 @@
         <v>-70.7</v>
       </c>
     </row>
-    <row r="131" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="131" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A131" s="5">
         <v>41609</v>
       </c>
@@ -8152,7 +8152,7 @@
         <v>-54.2</v>
       </c>
     </row>
-    <row r="132" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="132" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A132" s="10">
         <v>41579</v>
       </c>
@@ -8205,7 +8205,7 @@
         <v>-50.5</v>
       </c>
     </row>
-    <row r="133" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="133" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A133" s="5">
         <v>41548</v>
       </c>
@@ -8258,7 +8258,7 @@
         <v>-47.7</v>
       </c>
     </row>
-    <row r="134" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="134" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A134" s="10">
         <v>41518</v>
       </c>
@@ -8311,7 +8311,7 @@
         <v>-49.6</v>
       </c>
     </row>
-    <row r="135" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="135" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A135" s="5">
         <v>41487</v>
       </c>
@@ -8364,7 +8364,7 @@
         <v>-51</v>
       </c>
     </row>
-    <row r="136" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="136" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A136" s="10">
         <v>41456</v>
       </c>
@@ -8417,7 +8417,7 @@
         <v>-51.6</v>
       </c>
     </row>
-    <row r="137" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="137" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A137" s="5">
         <v>41426</v>
       </c>
@@ -8470,7 +8470,7 @@
         <v>-43.6</v>
       </c>
     </row>
-    <row r="138" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="138" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A138" s="10">
         <v>41395</v>
       </c>
@@ -8523,7 +8523,7 @@
         <v>-30.4</v>
       </c>
     </row>
-    <row r="139" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="139" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A139" s="5">
         <v>41365</v>
       </c>
@@ -8576,7 +8576,7 @@
         <v>-22.1</v>
       </c>
     </row>
-    <row r="140" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="140" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A140" s="10">
         <v>41334</v>
       </c>
@@ -8629,7 +8629,7 @@
         <v>-7.42</v>
       </c>
     </row>
-    <row r="141" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="141" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A141" s="5">
         <v>41306</v>
       </c>
@@ -8682,7 +8682,7 @@
         <v>12.9</v>
       </c>
     </row>
-    <row r="142" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="142" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A142" s="10">
         <v>41275</v>
       </c>
@@ -8735,7 +8735,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="143" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="143" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A143" s="5">
         <v>41244</v>
       </c>
@@ -8788,7 +8788,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="144" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="144" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A144" s="10">
         <v>41214</v>
       </c>
@@ -8841,7 +8841,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="145" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="145" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A145" s="5">
         <v>41183</v>
       </c>
@@ -8894,7 +8894,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="146" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="146" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A146" s="10">
         <v>41153</v>
       </c>
@@ -8947,7 +8947,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="147" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="147" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A147" s="5">
         <v>41122</v>
       </c>
@@ -9000,7 +9000,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="148" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="148" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A148" s="10">
         <v>41091</v>
       </c>
@@ -9053,7 +9053,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="149" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="149" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A149" s="5">
         <v>41061</v>
       </c>
@@ -9106,7 +9106,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="150" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="150" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A150" s="10">
         <v>41030</v>
       </c>
@@ -9159,7 +9159,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="151" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="151" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A151" s="5">
         <v>41000</v>
       </c>
@@ -9212,7 +9212,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="152" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="152" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A152" s="10">
         <v>40969</v>
       </c>
@@ -9265,7 +9265,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="153" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="153" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A153" s="5">
         <v>40940</v>
       </c>
@@ -9318,7 +9318,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="154" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="154" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A154" s="10">
         <v>40909</v>
       </c>
@@ -9371,7 +9371,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="155" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="155" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A155" s="5">
         <v>40878</v>
       </c>
@@ -9424,7 +9424,7 @@
         <v>52.3</v>
       </c>
     </row>
-    <row r="156" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="156" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A156" s="10">
         <v>40848</v>
       </c>
@@ -9477,7 +9477,7 @@
         <v>54.9</v>
       </c>
     </row>
-    <row r="157" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="157" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A157" s="5">
         <v>40817</v>
       </c>
@@ -9530,7 +9530,7 @@
         <v>56.2</v>
       </c>
     </row>
-    <row r="158" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="158" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A158" s="10">
         <v>40787</v>
       </c>
@@ -9583,7 +9583,7 @@
         <v>63.6</v>
       </c>
     </row>
-    <row r="159" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="159" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A159" s="5">
         <v>40756</v>
       </c>
@@ -9636,7 +9636,7 @@
         <v>68.099999999999994</v>
       </c>
     </row>
-    <row r="160" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="160" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A160" s="10">
         <v>40725</v>
       </c>
@@ -9689,7 +9689,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="161" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="161" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A161" s="5">
         <v>40695</v>
       </c>
@@ -9742,7 +9742,7 @@
         <v>60.7</v>
       </c>
     </row>
-    <row r="162" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="162" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A162" s="10">
         <v>40664</v>
       </c>
@@ -9795,7 +9795,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="163" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="163" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A163" s="5">
         <v>40634</v>
       </c>
@@ -9848,7 +9848,7 @@
         <v>64.2</v>
       </c>
     </row>
-    <row r="164" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="164" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A164" s="10">
         <v>40603</v>
       </c>
@@ -9901,7 +9901,7 @@
         <v>55.9</v>
       </c>
     </row>
-    <row r="165" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="165" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A165" s="5">
         <v>40575</v>
       </c>
@@ -9954,7 +9954,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="166" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="166" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A166" s="10">
         <v>40544</v>
       </c>
@@ -10007,7 +10007,7 @@
         <v>117.1</v>
       </c>
     </row>
-    <row r="167" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="167" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A167" s="5">
         <v>40513</v>
       </c>
@@ -10060,7 +10060,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="168" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="168" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A168" s="10">
         <v>40483</v>
       </c>
@@ -10113,7 +10113,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="169" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="169" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A169" s="5">
         <v>40452</v>
       </c>
@@ -10166,7 +10166,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="170" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="170" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A170" s="10">
         <v>40422</v>
       </c>
@@ -10219,7 +10219,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="171" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="171" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A171" s="5">
         <v>40391</v>
       </c>
@@ -10272,7 +10272,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="172" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="172" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A172" s="10">
         <v>40360</v>
       </c>
@@ -10325,7 +10325,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="173" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="173" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A173" s="5">
         <v>40330</v>
       </c>
@@ -10378,7 +10378,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="174" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="174" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A174" s="10">
         <v>40299</v>
       </c>
@@ -10431,7 +10431,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="175" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="175" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A175" s="5">
         <v>40269</v>
       </c>
@@ -10484,7 +10484,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="176" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="176" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A176" s="10">
         <v>40238</v>
       </c>
@@ -10537,7 +10537,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="177" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="177" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A177" s="5">
         <v>40210</v>
       </c>
@@ -10590,7 +10590,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="178" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="178" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A178" s="10">
         <v>40179</v>
       </c>
@@ -10643,7 +10643,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="179" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="179" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A179" s="5">
         <v>40148</v>
       </c>
@@ -10696,7 +10696,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="180" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="180" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A180" s="10">
         <v>40118</v>
       </c>
@@ -10749,932 +10749,932 @@
         <v>17</v>
       </c>
     </row>
-    <row r="181" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="181" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A181" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="182" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="182" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A182" s="5">
         <v>45444</v>
       </c>
     </row>
-    <row r="183" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="183" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A183" s="10">
         <v>45413</v>
       </c>
     </row>
-    <row r="184" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="184" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A184" s="5">
         <v>45383</v>
       </c>
     </row>
-    <row r="185" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="185" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A185" s="10">
         <v>45352</v>
       </c>
     </row>
-    <row r="186" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="186" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A186" s="5">
         <v>45323</v>
       </c>
     </row>
-    <row r="187" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="187" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A187" s="10">
         <v>45292</v>
       </c>
     </row>
-    <row r="188" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="188" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A188" s="5">
         <v>45261</v>
       </c>
     </row>
-    <row r="189" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="189" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A189" s="10">
         <v>45231</v>
       </c>
     </row>
-    <row r="190" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="190" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A190" s="5">
         <v>45200</v>
       </c>
     </row>
-    <row r="191" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="191" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A191" s="10">
         <v>45170</v>
       </c>
     </row>
-    <row r="192" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="192" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A192" s="5">
         <v>45139</v>
       </c>
     </row>
-    <row r="193" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="193" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A193" s="10">
         <v>45108</v>
       </c>
     </row>
-    <row r="194" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="194" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A194" s="5">
         <v>45078</v>
       </c>
     </row>
-    <row r="195" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="195" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A195" s="10">
         <v>45047</v>
       </c>
     </row>
-    <row r="196" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="196" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A196" s="5">
         <v>45017</v>
       </c>
     </row>
-    <row r="197" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="197" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A197" s="10">
         <v>44986</v>
       </c>
     </row>
-    <row r="198" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="198" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A198" s="5">
         <v>44958</v>
       </c>
     </row>
-    <row r="199" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="199" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A199" s="10">
         <v>44927</v>
       </c>
     </row>
-    <row r="200" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="200" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A200" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="201" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="201" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A201" s="5">
         <v>44896</v>
       </c>
     </row>
-    <row r="202" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="202" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A202" s="10">
         <v>44866</v>
       </c>
     </row>
-    <row r="203" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="203" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A203" s="5">
         <v>44835</v>
       </c>
     </row>
-    <row r="204" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="204" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A204" s="10">
         <v>44805</v>
       </c>
     </row>
-    <row r="205" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="205" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A205" s="5">
         <v>44774</v>
       </c>
     </row>
-    <row r="206" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="206" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A206" s="10">
         <v>44743</v>
       </c>
     </row>
-    <row r="207" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="207" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A207" s="5">
         <v>44713</v>
       </c>
     </row>
-    <row r="208" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="208" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A208" s="10">
         <v>44682</v>
       </c>
     </row>
-    <row r="209" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="209" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A209" s="5">
         <v>44652</v>
       </c>
     </row>
-    <row r="210" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="210" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A210" s="10">
         <v>44621</v>
       </c>
     </row>
-    <row r="211" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="211" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A211" s="5">
         <v>44593</v>
       </c>
     </row>
-    <row r="212" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="212" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A212" s="10">
         <v>44562</v>
       </c>
     </row>
-    <row r="213" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="213" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A213" s="5">
         <v>44531</v>
       </c>
     </row>
-    <row r="214" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="214" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A214" s="10">
         <v>44501</v>
       </c>
     </row>
-    <row r="215" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="215" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A215" s="5">
         <v>44470</v>
       </c>
     </row>
-    <row r="216" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="216" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A216" s="10">
         <v>44440</v>
       </c>
     </row>
-    <row r="217" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="217" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A217" s="5">
         <v>44409</v>
       </c>
     </row>
-    <row r="218" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="218" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A218" s="10">
         <v>44378</v>
       </c>
     </row>
-    <row r="219" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="219" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A219" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="220" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="220" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A220" s="5">
         <v>44348</v>
       </c>
     </row>
-    <row r="221" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="221" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A221" s="10">
         <v>44317</v>
       </c>
     </row>
-    <row r="222" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="222" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A222" s="5">
         <v>44287</v>
       </c>
     </row>
-    <row r="223" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="223" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A223" s="10">
         <v>44256</v>
       </c>
     </row>
-    <row r="224" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="224" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A224" s="5">
         <v>44228</v>
       </c>
     </row>
-    <row r="225" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="225" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A225" s="10">
         <v>44197</v>
       </c>
     </row>
-    <row r="226" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="226" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A226" s="5">
         <v>44166</v>
       </c>
     </row>
-    <row r="227" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="227" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A227" s="10">
         <v>44136</v>
       </c>
     </row>
-    <row r="228" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="228" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A228" s="5">
         <v>44105</v>
       </c>
     </row>
-    <row r="229" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="229" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A229" s="10">
         <v>44075</v>
       </c>
     </row>
-    <row r="230" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="230" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A230" s="5">
         <v>44044</v>
       </c>
     </row>
-    <row r="231" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="231" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A231" s="10">
         <v>44013</v>
       </c>
     </row>
-    <row r="232" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="232" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A232" s="5">
         <v>43983</v>
       </c>
     </row>
-    <row r="233" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="233" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A233" s="10">
         <v>43952</v>
       </c>
     </row>
-    <row r="234" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="234" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A234" s="5">
         <v>43922</v>
       </c>
     </row>
-    <row r="235" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="235" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A235" s="10">
         <v>43891</v>
       </c>
     </row>
-    <row r="236" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="236" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A236" s="5">
         <v>43862</v>
       </c>
     </row>
-    <row r="237" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="237" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A237" s="10">
         <v>43831</v>
       </c>
     </row>
-    <row r="238" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="238" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A238" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="239" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="239" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A239" s="5">
         <v>43800</v>
       </c>
     </row>
-    <row r="240" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="240" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A240" s="10">
         <v>43770</v>
       </c>
     </row>
-    <row r="241" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="241" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A241" s="5">
         <v>43739</v>
       </c>
     </row>
-    <row r="242" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="242" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A242" s="10">
         <v>43709</v>
       </c>
     </row>
-    <row r="243" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="243" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A243" s="5">
         <v>43678</v>
       </c>
     </row>
-    <row r="244" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="244" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A244" s="10">
         <v>43647</v>
       </c>
     </row>
-    <row r="245" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="245" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A245" s="5">
         <v>43617</v>
       </c>
     </row>
-    <row r="246" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="246" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A246" s="10">
         <v>43586</v>
       </c>
     </row>
-    <row r="247" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="247" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A247" s="5">
         <v>43556</v>
       </c>
     </row>
-    <row r="248" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="248" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A248" s="10">
         <v>43525</v>
       </c>
     </row>
-    <row r="249" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="249" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A249" s="5">
         <v>43497</v>
       </c>
     </row>
-    <row r="250" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="250" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A250" s="10">
         <v>43466</v>
       </c>
     </row>
-    <row r="251" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="251" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A251" s="5">
         <v>43435</v>
       </c>
     </row>
-    <row r="252" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="252" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A252" s="10">
         <v>43405</v>
       </c>
     </row>
-    <row r="253" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="253" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A253" s="5">
         <v>43374</v>
       </c>
     </row>
-    <row r="254" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="254" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A254" s="10">
         <v>43344</v>
       </c>
     </row>
-    <row r="255" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="255" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A255" s="5">
         <v>43313</v>
       </c>
     </row>
-    <row r="256" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="256" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A256" s="10">
         <v>43282</v>
       </c>
     </row>
-    <row r="257" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="257" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A257" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="258" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="258" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A258" s="5">
         <v>43252</v>
       </c>
     </row>
-    <row r="259" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="259" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A259" s="10">
         <v>43221</v>
       </c>
     </row>
-    <row r="260" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="260" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A260" s="5">
         <v>43191</v>
       </c>
     </row>
-    <row r="261" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="261" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A261" s="10">
         <v>43160</v>
       </c>
     </row>
-    <row r="262" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="262" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A262" s="5">
         <v>43132</v>
       </c>
     </row>
-    <row r="263" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="263" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A263" s="10">
         <v>43101</v>
       </c>
     </row>
-    <row r="264" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="264" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A264" s="5">
         <v>43070</v>
       </c>
     </row>
-    <row r="265" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="265" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A265" s="10">
         <v>43040</v>
       </c>
     </row>
-    <row r="266" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="266" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A266" s="5">
         <v>43009</v>
       </c>
     </row>
-    <row r="267" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="267" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A267" s="10">
         <v>42979</v>
       </c>
     </row>
-    <row r="268" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="268" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A268" s="5">
         <v>42948</v>
       </c>
     </row>
-    <row r="269" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="269" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A269" s="10">
         <v>42917</v>
       </c>
     </row>
-    <row r="270" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="270" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A270" s="5">
         <v>42887</v>
       </c>
     </row>
-    <row r="271" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="271" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A271" s="10">
         <v>42856</v>
       </c>
     </row>
-    <row r="272" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="272" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A272" s="5">
         <v>42826</v>
       </c>
     </row>
-    <row r="273" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="273" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A273" s="10">
         <v>42795</v>
       </c>
     </row>
-    <row r="274" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="274" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A274" s="5">
         <v>42767</v>
       </c>
     </row>
-    <row r="275" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="275" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A275" s="10">
         <v>42736</v>
       </c>
     </row>
-    <row r="276" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="276" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A276" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="277" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="277" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A277" s="5">
         <v>42705</v>
       </c>
     </row>
-    <row r="278" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="278" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A278" s="10">
         <v>42675</v>
       </c>
     </row>
-    <row r="279" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="279" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A279" s="5">
         <v>42644</v>
       </c>
     </row>
-    <row r="280" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="280" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A280" s="10">
         <v>42614</v>
       </c>
     </row>
-    <row r="281" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="281" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A281" s="5">
         <v>42583</v>
       </c>
     </row>
-    <row r="282" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="282" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A282" s="10">
         <v>42552</v>
       </c>
     </row>
-    <row r="283" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="283" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A283" s="5">
         <v>42522</v>
       </c>
     </row>
-    <row r="284" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="284" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A284" s="10">
         <v>42491</v>
       </c>
     </row>
-    <row r="285" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="285" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A285" s="5">
         <v>42461</v>
       </c>
     </row>
-    <row r="286" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="286" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A286" s="10">
         <v>42430</v>
       </c>
     </row>
-    <row r="287" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="287" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A287" s="5">
         <v>42401</v>
       </c>
     </row>
-    <row r="288" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="288" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A288" s="10">
         <v>42370</v>
       </c>
     </row>
-    <row r="289" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="289" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A289" s="5">
         <v>42339</v>
       </c>
     </row>
-    <row r="290" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="290" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A290" s="10">
         <v>42309</v>
       </c>
     </row>
-    <row r="291" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="291" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A291" s="5">
         <v>42278</v>
       </c>
     </row>
-    <row r="292" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="292" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A292" s="10">
         <v>42248</v>
       </c>
     </row>
-    <row r="293" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="293" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A293" s="5">
         <v>42217</v>
       </c>
     </row>
-    <row r="294" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="294" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A294" s="10">
         <v>42186</v>
       </c>
     </row>
-    <row r="295" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="295" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A295" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="296" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="296" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A296" s="5">
         <v>42156</v>
       </c>
     </row>
-    <row r="297" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="297" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A297" s="10">
         <v>42125</v>
       </c>
     </row>
-    <row r="298" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="298" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A298" s="5">
         <v>42095</v>
       </c>
     </row>
-    <row r="299" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="299" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A299" s="10">
         <v>42064</v>
       </c>
     </row>
-    <row r="300" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="300" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A300" s="5">
         <v>42036</v>
       </c>
     </row>
-    <row r="301" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="301" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A301" s="10">
         <v>42005</v>
       </c>
     </row>
-    <row r="302" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="302" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A302" s="5">
         <v>41974</v>
       </c>
     </row>
-    <row r="303" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="303" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A303" s="10">
         <v>41944</v>
       </c>
     </row>
-    <row r="304" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="304" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A304" s="5">
         <v>41913</v>
       </c>
     </row>
-    <row r="305" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="305" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A305" s="10">
         <v>41883</v>
       </c>
     </row>
-    <row r="306" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="306" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A306" s="5">
         <v>41852</v>
       </c>
     </row>
-    <row r="307" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="307" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A307" s="10">
         <v>41821</v>
       </c>
     </row>
-    <row r="308" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="308" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A308" s="5">
         <v>41791</v>
       </c>
     </row>
-    <row r="309" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="309" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A309" s="10">
         <v>41760</v>
       </c>
     </row>
-    <row r="310" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="310" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A310" s="5">
         <v>41730</v>
       </c>
     </row>
-    <row r="311" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="311" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A311" s="10">
         <v>41699</v>
       </c>
     </row>
-    <row r="312" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="312" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A312" s="5">
         <v>41671</v>
       </c>
     </row>
-    <row r="313" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="313" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A313" s="10">
         <v>41640</v>
       </c>
     </row>
-    <row r="314" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="314" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A314" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="315" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="315" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A315" s="5">
         <v>41609</v>
       </c>
     </row>
-    <row r="316" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="316" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A316" s="10">
         <v>41579</v>
       </c>
     </row>
-    <row r="317" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="317" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A317" s="5">
         <v>41548</v>
       </c>
     </row>
-    <row r="318" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="318" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A318" s="10">
         <v>41518</v>
       </c>
     </row>
-    <row r="319" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="319" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A319" s="5">
         <v>41487</v>
       </c>
     </row>
-    <row r="320" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="320" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A320" s="10">
         <v>41456</v>
       </c>
     </row>
-    <row r="321" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="321" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A321" s="5">
         <v>41426</v>
       </c>
     </row>
-    <row r="322" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="322" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A322" s="10">
         <v>41395</v>
       </c>
     </row>
-    <row r="323" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="323" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A323" s="5">
         <v>41365</v>
       </c>
     </row>
-    <row r="324" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="324" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A324" s="10">
         <v>41334</v>
       </c>
     </row>
-    <row r="325" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="325" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A325" s="5">
         <v>41306</v>
       </c>
     </row>
-    <row r="326" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="326" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A326" s="10">
         <v>41275</v>
       </c>
     </row>
-    <row r="327" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="327" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A327" s="5">
         <v>41244</v>
       </c>
     </row>
-    <row r="328" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="328" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A328" s="10">
         <v>41214</v>
       </c>
     </row>
-    <row r="329" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="329" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A329" s="5">
         <v>41183</v>
       </c>
     </row>
-    <row r="330" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="330" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A330" s="10">
         <v>41153</v>
       </c>
     </row>
-    <row r="331" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="331" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A331" s="5">
         <v>41122</v>
       </c>
     </row>
-    <row r="332" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="332" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A332" s="10">
         <v>41091</v>
       </c>
     </row>
-    <row r="333" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="333" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A333" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="334" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="334" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A334" s="5">
         <v>41061</v>
       </c>
     </row>
-    <row r="335" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="335" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A335" s="10">
         <v>41030</v>
       </c>
     </row>
-    <row r="336" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="336" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A336" s="5">
         <v>41000</v>
       </c>
     </row>
-    <row r="337" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="337" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A337" s="10">
         <v>40969</v>
       </c>
     </row>
-    <row r="338" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="338" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A338" s="5">
         <v>40940</v>
       </c>
     </row>
-    <row r="339" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="339" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A339" s="10">
         <v>40909</v>
       </c>
     </row>
-    <row r="340" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="340" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A340" s="5">
         <v>40878</v>
       </c>
     </row>
-    <row r="341" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="341" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A341" s="10">
         <v>40848</v>
       </c>
     </row>
-    <row r="342" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="342" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A342" s="5">
         <v>40817</v>
       </c>
     </row>
-    <row r="343" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="343" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A343" s="10">
         <v>40787</v>
       </c>
     </row>
-    <row r="344" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="344" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A344" s="5">
         <v>40756</v>
       </c>
     </row>
-    <row r="345" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="345" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A345" s="10">
         <v>40725</v>
       </c>
     </row>
-    <row r="346" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="346" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A346" s="5">
         <v>40695</v>
       </c>
     </row>
-    <row r="347" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="347" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A347" s="10">
         <v>40664</v>
       </c>
     </row>
-    <row r="348" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="348" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A348" s="5">
         <v>40634</v>
       </c>
     </row>
-    <row r="349" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="349" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A349" s="10">
         <v>40603</v>
       </c>
     </row>
-    <row r="350" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="350" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A350" s="5">
         <v>40575</v>
       </c>
     </row>
-    <row r="351" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="351" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A351" s="10">
         <v>40544</v>
       </c>
     </row>
-    <row r="352" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="352" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A352" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="353" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="353" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A353" s="5">
         <v>40513</v>
       </c>
     </row>
-    <row r="354" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="354" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A354" s="10">
         <v>40483</v>
       </c>
     </row>
-    <row r="355" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="355" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A355" s="5">
         <v>40452</v>
       </c>
     </row>
-    <row r="356" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="356" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A356" s="10">
         <v>40422</v>
       </c>
     </row>
-    <row r="357" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="357" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A357" s="5">
         <v>40391</v>
       </c>
     </row>
-    <row r="358" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="358" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A358" s="10">
         <v>40360</v>
       </c>
     </row>
-    <row r="359" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="359" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A359" s="5">
         <v>40330</v>
       </c>
     </row>
-    <row r="360" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="360" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A360" s="10">
         <v>40299</v>
       </c>
     </row>
-    <row r="361" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="361" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A361" s="5">
         <v>40269</v>
       </c>
     </row>
-    <row r="362" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="362" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A362" s="10">
         <v>40238</v>
       </c>
     </row>
-    <row r="363" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="363" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A363" s="5">
         <v>40210</v>
       </c>
     </row>
-    <row r="364" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="364" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A364" s="10">
         <v>40179</v>
       </c>
     </row>
-    <row r="365" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="365" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A365" s="5">
         <v>40148</v>
       </c>
     </row>
-    <row r="366" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="366" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A366" s="10">
         <v>40118</v>
       </c>
